--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_37.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1574643.175830425</v>
+        <v>1579108.624284395</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5413711.842050619</v>
+        <v>5148253.621372774</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11300164.78834108</v>
+        <v>11194959.33207959</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6356348.896967388</v>
+        <v>6408300.434847618</v>
       </c>
     </row>
     <row r="11">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2286,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>20.22272895978741</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
     </row>
     <row r="23">
@@ -2353,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>20.22272895978741</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2396,13 +2396,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2517,13 +2517,13 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
     </row>
     <row r="26">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2593,10 +2593,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
     </row>
     <row r="27">
@@ -2630,16 +2630,16 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>20.34341911851555</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2788,10 +2788,10 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
     </row>
     <row r="30">
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2912,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
     </row>
     <row r="31">
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>12.14519810006681</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2988,13 +2988,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3034,10 +3034,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7.697128181848378</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -3073,10 +3073,10 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3146,19 +3146,19 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3307,16 +3307,16 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>20.22272895978741</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3341,10 +3341,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>15.15497198123338</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
     </row>
     <row r="39">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3663,13 +3663,13 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>13.80331688454756</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3736,13 +3736,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>20.22272895978742</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3784,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>20.22272895978741</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3897,16 +3897,16 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>20.02682021433313</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.1959087454542976</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>24.90626657308192</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>14.10463699225912</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>14.10463699225912</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>9.61163707486676</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>79.18588417731982</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>79.18588417731982</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>79.18588417731982</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>55.99446847650213</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>32.80305277568445</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>30.14712226730633</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>30.14712226730633</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>30.14712226730633</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>9.640492679235312</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>70.02647970861901</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>53.33853796812402</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>30.14712226730633</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>30.14712226730633</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>22.26375907278499</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>57.26077647946913</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>57.26077647946913</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>57.26077647946913</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>43.31803215164331</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>20.12661645082562</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>24.56666665187618</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>47.29657318024759</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>71.41100722595783</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>48.21959152514014</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>25.22606344599346</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>25.22606344599346</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>25.02817582432245</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1.836760123504761</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>23.6482865901238</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>46.37819311849522</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>69.10809964686663</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>91.83800617523805</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>68.64659047442036</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>45.45517477360268</v>
       </c>
     </row>
     <row r="44">
@@ -9381,19 +9381,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>220.0898510449805</v>
+        <v>243.0493525887901</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M20" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>229.4130635965909</v>
+        <v>252.3725651404004</v>
       </c>
       <c r="O20" t="n">
-        <v>230.0982114216867</v>
+        <v>252.1300563374635</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -9463,16 +9463,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>160.586224695651</v>
       </c>
       <c r="M21" t="n">
-        <v>142.1340339220183</v>
+        <v>165.0935354658278</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>154.3012136271428</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444444</v>
+        <v>165.555745988254</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
@@ -9542,16 +9542,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>134.8846762812383</v>
+        <v>157.8441778250478</v>
       </c>
       <c r="M22" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N22" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O22" t="n">
-        <v>138.4565384518428</v>
+        <v>160.4883833676196</v>
       </c>
       <c r="P22" t="n">
         <v>135.0065633140411</v>
@@ -9618,16 +9618,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>220.0898510449805</v>
+        <v>243.0493525887901</v>
       </c>
       <c r="L23" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M23" t="n">
-        <v>230.3462332272727</v>
+        <v>253.3057347710823</v>
       </c>
       <c r="N23" t="n">
-        <v>229.4130635965909</v>
+        <v>251.4449085123677</v>
       </c>
       <c r="O23" t="n">
         <v>230.0982114216867</v>
@@ -9706,16 +9706,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>131.3417120833333</v>
+        <v>153.3735569991101</v>
       </c>
       <c r="O24" t="n">
-        <v>142.5962444444444</v>
+        <v>165.555745988254</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>156.9339089581398</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>162.941275629831</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9779,16 +9779,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>134.8846762812383</v>
+        <v>157.8441778250478</v>
       </c>
       <c r="M25" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N25" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O25" t="n">
-        <v>138.4565384518428</v>
+        <v>160.4883833676196</v>
       </c>
       <c r="P25" t="n">
         <v>135.0065633140411</v>
@@ -9861,16 +9861,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>252.3780781430495</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>252.3725651404004</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>253.0577129654963</v>
       </c>
       <c r="P26" t="n">
-        <v>231.2329957552695</v>
+        <v>254.1924972990791</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9940,16 +9940,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>165.0935354658278</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>154.3012136271428</v>
       </c>
       <c r="O27" t="n">
-        <v>142.5962444444444</v>
+        <v>165.555745988254</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>156.0062523301071</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10016,16 +10016,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>134.8846762812383</v>
+        <v>156.9165211970151</v>
       </c>
       <c r="M28" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N28" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O28" t="n">
-        <v>138.4565384518428</v>
+        <v>161.4160399956523</v>
       </c>
       <c r="P28" t="n">
         <v>135.0065633140411</v>
@@ -10092,16 +10092,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>242.1216959607574</v>
       </c>
       <c r="L29" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M29" t="n">
-        <v>230.3462332272727</v>
+        <v>253.3057347710823</v>
       </c>
       <c r="N29" t="n">
-        <v>229.4130635965909</v>
+        <v>252.3725651404004</v>
       </c>
       <c r="O29" t="n">
         <v>230.0982114216867</v>
@@ -10180,16 +10180,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>153.3735569991101</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>165.555745988254</v>
       </c>
       <c r="P30" t="n">
-        <v>133.9744074143302</v>
+        <v>156.9339089581398</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>162.941275629831</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,16 +10253,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>134.8846762812383</v>
+        <v>156.9165211970151</v>
       </c>
       <c r="M31" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O31" t="n">
-        <v>138.4565384518428</v>
+        <v>161.4160399956523</v>
       </c>
       <c r="P31" t="n">
         <v>135.0065633140411</v>
@@ -10329,16 +10329,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>220.0898510449805</v>
+        <v>243.0493525887901</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>253.3057347710823</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635965909</v>
+        <v>251.4449085123677</v>
       </c>
       <c r="O32" t="n">
         <v>230.0982114216867</v>
@@ -10417,16 +10417,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>153.3735569991101</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>165.555745988254</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>156.9339089581398</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>162.941275629831</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10490,16 +10490,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>134.8846762812383</v>
+        <v>156.9165211970151</v>
       </c>
       <c r="M34" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N34" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O34" t="n">
-        <v>138.4565384518428</v>
+        <v>161.4160399956523</v>
       </c>
       <c r="P34" t="n">
         <v>135.0065633140411</v>
@@ -10569,16 +10569,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>252.3780781430495</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>252.3725651404004</v>
       </c>
       <c r="O35" t="n">
-        <v>230.0982114216867</v>
+        <v>253.0577129654963</v>
       </c>
       <c r="P35" t="n">
         <v>231.2329957552695</v>
@@ -10648,19 +10648,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>161.5138813236837</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>165.0935354658278</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>154.3012136271428</v>
       </c>
       <c r="O36" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>156.0062523301071</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10727,16 +10727,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>134.8846762812383</v>
+        <v>156.9165211970151</v>
       </c>
       <c r="M37" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N37" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O37" t="n">
-        <v>138.4565384518428</v>
+        <v>161.4160399956523</v>
       </c>
       <c r="P37" t="n">
         <v>135.0065633140411</v>
@@ -10803,19 +10803,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>220.0898510449805</v>
+        <v>243.0493525887901</v>
       </c>
       <c r="L38" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M38" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635965909</v>
+        <v>251.4449085123677</v>
       </c>
       <c r="O38" t="n">
-        <v>230.0982114216867</v>
+        <v>253.0577129654963</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10885,22 +10885,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>161.5138813236837</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>165.0935354658278</v>
       </c>
       <c r="N39" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>142.5962444444444</v>
+        <v>164.6280893602213</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>139.9817740860215</v>
+        <v>162.941275629831</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10964,16 +10964,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>134.8846762812383</v>
+        <v>156.9165211970151</v>
       </c>
       <c r="M40" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N40" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O40" t="n">
-        <v>138.4565384518428</v>
+        <v>161.4160399956523</v>
       </c>
       <c r="P40" t="n">
         <v>135.0065633140411</v>
@@ -11043,16 +11043,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>235.7664149699872</v>
+        <v>258.7259165137967</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>253.3057347710823</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635965909</v>
+        <v>251.4449085123677</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>253.0577129654963</v>
       </c>
       <c r="P41" t="n">
         <v>231.2329957552695</v>
@@ -11119,13 +11119,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>159.8732838901358</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>161.5138813236837</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>165.0935354658278</v>
       </c>
       <c r="N42" t="n">
         <v>131.3417120833333</v>
@@ -11134,7 +11134,7 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>156.9339089581398</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -11201,16 +11201,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>134.8846762812383</v>
+        <v>156.9165211970151</v>
       </c>
       <c r="M43" t="n">
-        <v>138.9257839476051</v>
+        <v>161.8852854914146</v>
       </c>
       <c r="N43" t="n">
-        <v>127.6855444652332</v>
+        <v>150.6450460090427</v>
       </c>
       <c r="O43" t="n">
-        <v>138.4565384518428</v>
+        <v>161.4160399956523</v>
       </c>
       <c r="P43" t="n">
         <v>135.0065633140411</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.876045741711209</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
-        <v>15.30273751513482</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22753,10 +22753,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>15.30273751513494</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22990,10 +22990,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.87604574171138</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>15.30273751513499</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>360.7338416634806</v>
+        <v>370.7845523088681</v>
       </c>
       <c r="C11" t="n">
-        <v>343.2728917710076</v>
+        <v>353.323602416395</v>
       </c>
       <c r="D11" t="n">
-        <v>332.683041620683</v>
+        <v>342.7337522660704</v>
       </c>
       <c r="E11" t="n">
-        <v>359.9303700722618</v>
+        <v>369.9810807176493</v>
       </c>
       <c r="F11" t="n">
-        <v>384.8760457417114</v>
+        <v>394.9267563870989</v>
       </c>
       <c r="G11" t="n">
-        <v>393.302737515135</v>
+        <v>403.3534481605225</v>
       </c>
       <c r="H11" t="n">
-        <v>317.4748021157671</v>
+        <v>327.5255127611546</v>
       </c>
       <c r="I11" t="n">
-        <v>188.4758895704059</v>
+        <v>198.5266002157934</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>127.8691179411497</v>
+        <v>137.9198285865372</v>
       </c>
       <c r="S11" t="n">
-        <v>187.0200695862453</v>
+        <v>197.0707802316328</v>
       </c>
       <c r="T11" t="n">
-        <v>201.0958495641314</v>
+        <v>211.1465602095188</v>
       </c>
       <c r="U11" t="n">
-        <v>229.3456529078365</v>
+        <v>239.396363553224</v>
       </c>
       <c r="V11" t="n">
-        <v>305.7522584701349</v>
+        <v>315.8029691155224</v>
       </c>
       <c r="W11" t="n">
-        <v>327.240968717413</v>
+        <v>337.2916793628005</v>
       </c>
       <c r="X11" t="n">
-        <v>347.731100678469</v>
+        <v>357.7818113238565</v>
       </c>
       <c r="Y11" t="n">
-        <v>364.2379386560536</v>
+        <v>374.2886493014411</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144.5331836498673</v>
+        <v>154.5838942952548</v>
       </c>
       <c r="C12" t="n">
-        <v>150.7084989883157</v>
+        <v>160.7592096337032</v>
       </c>
       <c r="D12" t="n">
-        <v>125.4450655646388</v>
+        <v>135.4957762100262</v>
       </c>
       <c r="E12" t="n">
-        <v>135.6450804554009</v>
+        <v>145.6957911007884</v>
       </c>
       <c r="F12" t="n">
-        <v>123.0692123933839</v>
+        <v>133.1199230387714</v>
       </c>
       <c r="G12" t="n">
-        <v>115.3435171632106</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H12" t="n">
-        <v>90.23544423649646</v>
+        <v>100.2861548818839</v>
       </c>
       <c r="I12" t="n">
-        <v>67.39663285141508</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.15783415264313</v>
+        <v>88.20854479803062</v>
       </c>
       <c r="S12" t="n">
-        <v>149.6831711038378</v>
+        <v>159.7338817492253</v>
       </c>
       <c r="T12" t="n">
-        <v>178.1647286948216</v>
+        <v>188.2154393402091</v>
       </c>
       <c r="U12" t="n">
-        <v>203.9413820809748</v>
+        <v>213.9920927263623</v>
       </c>
       <c r="V12" t="n">
-        <v>210.8005871494253</v>
+        <v>220.8512977948128</v>
       </c>
       <c r="W12" t="n">
-        <v>229.6949831609196</v>
+        <v>239.7456938063071</v>
       </c>
       <c r="X12" t="n">
-        <v>183.7729852034775</v>
+        <v>193.823695848865</v>
       </c>
       <c r="Y12" t="n">
-        <v>183.6826957773044</v>
+        <v>193.7334064226918</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>157.8319801819373</v>
+        <v>167.8826908273248</v>
       </c>
       <c r="C13" t="n">
-        <v>145.2468210986278</v>
+        <v>155.2975317440153</v>
       </c>
       <c r="D13" t="n">
-        <v>126.6154730182124</v>
+        <v>136.6661836635998</v>
       </c>
       <c r="E13" t="n">
-        <v>124.4339626465692</v>
+        <v>134.4846732919567</v>
       </c>
       <c r="F13" t="n">
-        <v>123.4210480229312</v>
+        <v>133.4717586683187</v>
       </c>
       <c r="G13" t="n">
-        <v>145.9909793584588</v>
+        <v>156.0416900038462</v>
       </c>
       <c r="H13" t="n">
-        <v>140.2271725074396</v>
+        <v>150.2778831528271</v>
       </c>
       <c r="I13" t="n">
-        <v>133.4504749272583</v>
+        <v>143.5011855726458</v>
       </c>
       <c r="J13" t="n">
-        <v>71.35918011667277</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2694918258828523</v>
+        <v>10.32020247127033</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.16204325169439</v>
+        <v>74.21275389708187</v>
       </c>
       <c r="R13" t="n">
-        <v>155.2933913771695</v>
+        <v>165.344102022557</v>
       </c>
       <c r="S13" t="n">
-        <v>202.0165980369723</v>
+        <v>212.0673086823597</v>
       </c>
       <c r="T13" t="n">
-        <v>205.9455894282815</v>
+        <v>215.996300073669</v>
       </c>
       <c r="U13" t="n">
-        <v>264.3190293564909</v>
+        <v>274.3697400018784</v>
       </c>
       <c r="V13" t="n">
-        <v>230.137643323828</v>
+        <v>240.1883539692155</v>
       </c>
       <c r="W13" t="n">
-        <v>264.522998336591</v>
+        <v>274.5737089819785</v>
       </c>
       <c r="X13" t="n">
-        <v>203.7096553890372</v>
+        <v>213.7603660344246</v>
       </c>
       <c r="Y13" t="n">
-        <v>196.5846533520948</v>
+        <v>206.6353639974823</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.8691179411497</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>270.377707268256</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>252.916757375783</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>245.0636798094805</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>96.66393519102076</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>27.72415535200813</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>59.32703670861324</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>87.80859429959702</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>93.41685080825289</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>142.5182815126255</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>174.1668639413664</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>113.3535209938126</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>106.2285189568702</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.86911794114968</v>
+        <v>40.24975612994719</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>110.7397151689068</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>138.9895185126119</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X23" t="n">
-        <v>275.731100678469</v>
+        <v>257.3749662832445</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>32.71307799815929</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>2.616082425293961</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>120.4444527542007</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>139.338848765695</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>115.5894550330569</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>173.9628949612663</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>139.7815089286034</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>108.9652915408923</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>292.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>275.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>264.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>291.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>316.8760457417114</v>
+        <v>297.2566839305089</v>
       </c>
       <c r="G26" t="n">
-        <v>325.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>249.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>120.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>59.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>119.0200695862453</v>
+        <v>96.66393519102076</v>
       </c>
       <c r="T26" t="n">
-        <v>133.0958495641314</v>
+        <v>110.7397151689068</v>
       </c>
       <c r="U26" t="n">
-        <v>161.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>237.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>259.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>279.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>296.2379386560536</v>
+        <v>273.881804260829</v>
       </c>
     </row>
     <row r="27">
@@ -24479,25 +24479,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>76.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>82.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>57.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>67.64508045540094</v>
+        <v>45.28894606017636</v>
       </c>
       <c r="F27" t="n">
-        <v>55.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>47.34351716321063</v>
+        <v>27.60346519328001</v>
       </c>
       <c r="H27" t="n">
-        <v>22.23544423649646</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>10.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>81.68317110383782</v>
+        <v>59.32703670861324</v>
       </c>
       <c r="T27" t="n">
-        <v>110.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>135.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>142.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>161.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>115.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>115.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>77.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>58.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>56.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>55.42104802293125</v>
+        <v>35.80168621172874</v>
       </c>
       <c r="G28" t="n">
-        <v>77.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>72.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>65.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>3.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>87.29339137716948</v>
+        <v>64.9372569819449</v>
       </c>
       <c r="S28" t="n">
-        <v>134.0165980369723</v>
+        <v>111.6604636417477</v>
       </c>
       <c r="T28" t="n">
-        <v>137.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>196.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>162.137643323828</v>
+        <v>139.7815089286034</v>
       </c>
       <c r="W28" t="n">
-        <v>196.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>135.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>128.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>244.7338416634806</v>
+        <v>225.1675955404825</v>
       </c>
       <c r="C29" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D29" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E29" t="n">
-        <v>243.9303700722618</v>
+        <v>221.6273513652416</v>
       </c>
       <c r="F29" t="n">
-        <v>268.8760457417114</v>
+        <v>246.5730270346913</v>
       </c>
       <c r="G29" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H29" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I29" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S29" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T29" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U29" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V29" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W29" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X29" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y29" t="n">
-        <v>248.2379386560536</v>
+        <v>225.9349199490334</v>
       </c>
     </row>
     <row r="30">
@@ -24716,19 +24716,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C30" t="n">
-        <v>34.70849898831574</v>
+        <v>15.14225286531768</v>
       </c>
       <c r="D30" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E30" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F30" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T30" t="n">
-        <v>62.1647286948216</v>
+        <v>39.86170998780146</v>
       </c>
       <c r="U30" t="n">
-        <v>87.94138208097482</v>
+        <v>65.63836337395468</v>
       </c>
       <c r="V30" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W30" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X30" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y30" t="n">
-        <v>67.68269577730436</v>
+        <v>45.37967707028422</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C31" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D31" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E31" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F31" t="n">
-        <v>7.421048022931245</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H31" t="n">
-        <v>24.22717250743958</v>
+        <v>12.73845724416213</v>
       </c>
       <c r="I31" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S31" t="n">
-        <v>86.01659803697225</v>
+        <v>63.71357932995211</v>
       </c>
       <c r="T31" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U31" t="n">
-        <v>148.3190293564909</v>
+        <v>126.0160106494707</v>
       </c>
       <c r="V31" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W31" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X31" t="n">
-        <v>87.70965538903715</v>
+        <v>65.40663668201701</v>
       </c>
       <c r="Y31" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C32" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D32" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E32" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F32" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G32" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H32" t="n">
-        <v>201.4748021157671</v>
+        <v>179.171783408747</v>
       </c>
       <c r="I32" t="n">
-        <v>72.47588957040591</v>
+        <v>65.43524422534689</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>11.86911794114968</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T32" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U32" t="n">
-        <v>113.3456529078365</v>
+        <v>91.04263420081635</v>
       </c>
       <c r="V32" t="n">
-        <v>189.7522584701349</v>
+        <v>167.4492397631147</v>
       </c>
       <c r="W32" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X32" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y32" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="33">
@@ -24953,19 +24953,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C33" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D33" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E33" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F33" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>33.68317110383782</v>
+        <v>11.38015239681767</v>
       </c>
       <c r="T33" t="n">
-        <v>62.1647286948216</v>
+        <v>39.86170998780146</v>
       </c>
       <c r="U33" t="n">
-        <v>87.94138208097482</v>
+        <v>65.63836337395468</v>
       </c>
       <c r="V33" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W33" t="n">
-        <v>113.6949831609196</v>
+        <v>94.12873703792155</v>
       </c>
       <c r="X33" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y33" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C34" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D34" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E34" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F34" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G34" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H34" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I34" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>39.29339137716948</v>
+        <v>16.99037267014934</v>
       </c>
       <c r="S34" t="n">
-        <v>86.01659803697225</v>
+        <v>66.4503519139742</v>
       </c>
       <c r="T34" t="n">
-        <v>89.94558942828149</v>
+        <v>67.64257072126135</v>
       </c>
       <c r="U34" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V34" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W34" t="n">
-        <v>148.522998336591</v>
+        <v>126.2199796295709</v>
       </c>
       <c r="X34" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y34" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>244.7338416634806</v>
+        <v>222.4308229564604</v>
       </c>
       <c r="C35" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D35" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E35" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F35" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G35" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H35" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I35" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S35" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T35" t="n">
-        <v>85.09584956413136</v>
+        <v>65.5296034411333</v>
       </c>
       <c r="U35" t="n">
-        <v>113.3456529078365</v>
+        <v>91.04263420081635</v>
       </c>
       <c r="V35" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W35" t="n">
-        <v>211.240968717413</v>
+        <v>188.9379500103929</v>
       </c>
       <c r="X35" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y35" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C36" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D36" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E36" t="n">
-        <v>19.64508045540094</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>7.069212393383879</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T36" t="n">
-        <v>62.1647286948216</v>
+        <v>39.86170998780146</v>
       </c>
       <c r="U36" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V36" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W36" t="n">
-        <v>113.6949831609196</v>
+        <v>99.1964940164756</v>
       </c>
       <c r="X36" t="n">
-        <v>67.77298520347748</v>
+        <v>45.46996649645733</v>
       </c>
       <c r="Y36" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.8319801819373</v>
+        <v>22.26573405893924</v>
       </c>
       <c r="C37" t="n">
-        <v>29.24682109862783</v>
+        <v>6.943802391607687</v>
       </c>
       <c r="D37" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E37" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F37" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G37" t="n">
-        <v>29.99097935845876</v>
+        <v>7.687960651438612</v>
       </c>
       <c r="H37" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I37" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>39.29339137716948</v>
+        <v>16.99037267014934</v>
       </c>
       <c r="S37" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T37" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U37" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V37" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W37" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X37" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y37" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>244.7338416634806</v>
+        <v>225.1675955404825</v>
       </c>
       <c r="C38" t="n">
-        <v>227.2728917710076</v>
+        <v>204.9698730639874</v>
       </c>
       <c r="D38" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E38" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F38" t="n">
-        <v>268.8760457417114</v>
+        <v>246.5730270346913</v>
       </c>
       <c r="G38" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H38" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I38" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S38" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T38" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U38" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V38" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W38" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X38" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y38" t="n">
-        <v>248.2379386560536</v>
+        <v>225.9349199490334</v>
       </c>
     </row>
     <row r="39">
@@ -25427,19 +25427,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.53318364986734</v>
+        <v>8.96693752686928</v>
       </c>
       <c r="C39" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D39" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E39" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F39" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>33.68317110383782</v>
+        <v>11.38015239681767</v>
       </c>
       <c r="T39" t="n">
-        <v>62.1647286948216</v>
+        <v>39.86170998780146</v>
       </c>
       <c r="U39" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V39" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W39" t="n">
-        <v>113.6949831609196</v>
+        <v>91.39196445389946</v>
       </c>
       <c r="X39" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y39" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C40" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D40" t="n">
-        <v>10.61547301821236</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F40" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G40" t="n">
-        <v>29.99097935845876</v>
+        <v>16.84414531070056</v>
       </c>
       <c r="H40" t="n">
-        <v>24.22717250743958</v>
+        <v>1.924153800419429</v>
       </c>
       <c r="I40" t="n">
-        <v>17.45047492725828</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>39.29339137716948</v>
+        <v>16.99037267014934</v>
       </c>
       <c r="S40" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T40" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U40" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V40" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W40" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X40" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y40" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>262.7338416634806</v>
+        <v>257.3396138548825</v>
       </c>
       <c r="C41" t="n">
-        <v>245.2728917710076</v>
+        <v>239.8786639624094</v>
       </c>
       <c r="D41" t="n">
-        <v>234.683041620683</v>
+        <v>229.2888138120848</v>
       </c>
       <c r="E41" t="n">
-        <v>261.9303700722618</v>
+        <v>236.3134133038763</v>
       </c>
       <c r="F41" t="n">
-        <v>286.8760457417114</v>
+        <v>258.5223163893039</v>
       </c>
       <c r="G41" t="n">
-        <v>295.302737515135</v>
+        <v>266.9490081627275</v>
       </c>
       <c r="H41" t="n">
-        <v>219.4748021157671</v>
+        <v>214.080574307169</v>
       </c>
       <c r="I41" t="n">
-        <v>90.47588957040591</v>
+        <v>85.08166176180779</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>29.86911794114968</v>
+        <v>24.47489013255156</v>
       </c>
       <c r="S41" t="n">
-        <v>89.02006958624534</v>
+        <v>83.62584177764722</v>
       </c>
       <c r="T41" t="n">
-        <v>103.0958495641314</v>
+        <v>97.70162175553324</v>
       </c>
       <c r="U41" t="n">
-        <v>131.3456529078365</v>
+        <v>102.9919235554289</v>
       </c>
       <c r="V41" t="n">
-        <v>207.7522584701349</v>
+        <v>202.3580306615368</v>
       </c>
       <c r="W41" t="n">
-        <v>229.240968717413</v>
+        <v>223.8467409088149</v>
       </c>
       <c r="X41" t="n">
-        <v>249.731100678469</v>
+        <v>244.3368728698709</v>
       </c>
       <c r="Y41" t="n">
-        <v>266.2379386560536</v>
+        <v>260.8437108474554</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>46.53318364986734</v>
+        <v>18.17945429745971</v>
       </c>
       <c r="C42" t="n">
-        <v>52.70849898831574</v>
+        <v>24.35476963590811</v>
       </c>
       <c r="D42" t="n">
-        <v>27.44506556463875</v>
+        <v>22.05083775604064</v>
       </c>
       <c r="E42" t="n">
-        <v>37.64508045540094</v>
+        <v>32.25085264680283</v>
       </c>
       <c r="F42" t="n">
-        <v>25.06921239338388</v>
+        <v>19.67498458478576</v>
       </c>
       <c r="G42" t="n">
-        <v>17.34351716321063</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>51.68317110383782</v>
+        <v>46.2889432952397</v>
       </c>
       <c r="T42" t="n">
-        <v>80.1647286948216</v>
+        <v>54.54777192643607</v>
       </c>
       <c r="U42" t="n">
-        <v>105.9413820809748</v>
+        <v>100.5471542723767</v>
       </c>
       <c r="V42" t="n">
-        <v>112.8005871494253</v>
+        <v>107.4063593408272</v>
       </c>
       <c r="W42" t="n">
-        <v>131.6949831609196</v>
+        <v>126.3007553523215</v>
       </c>
       <c r="X42" t="n">
-        <v>85.77298520347748</v>
+        <v>57.41925585106985</v>
       </c>
       <c r="Y42" t="n">
-        <v>85.68269577730436</v>
+        <v>80.28846796870624</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>59.8319801819373</v>
+        <v>54.43775237333918</v>
       </c>
       <c r="C43" t="n">
-        <v>47.24682109862783</v>
+        <v>41.85259329002972</v>
       </c>
       <c r="D43" t="n">
-        <v>28.61547301821236</v>
+        <v>23.22124520961424</v>
       </c>
       <c r="E43" t="n">
-        <v>26.43396264656917</v>
+        <v>21.03973483797105</v>
       </c>
       <c r="F43" t="n">
-        <v>25.42104802293125</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>47.99097935845876</v>
+        <v>42.59675154986064</v>
       </c>
       <c r="H43" t="n">
-        <v>42.22717250743958</v>
+        <v>36.63703595338716</v>
       </c>
       <c r="I43" t="n">
-        <v>35.45047492725828</v>
+        <v>7.096745574850654</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>57.29339137716948</v>
+        <v>28.93966202476186</v>
       </c>
       <c r="S43" t="n">
-        <v>104.0165980369723</v>
+        <v>98.62237022837414</v>
       </c>
       <c r="T43" t="n">
-        <v>107.9455894282815</v>
+        <v>102.5513616196834</v>
       </c>
       <c r="U43" t="n">
-        <v>166.3190293564909</v>
+        <v>160.9248015478928</v>
       </c>
       <c r="V43" t="n">
-        <v>132.137643323828</v>
+        <v>126.7434155152299</v>
       </c>
       <c r="W43" t="n">
-        <v>166.522998336591</v>
+        <v>161.1287705279929</v>
       </c>
       <c r="X43" t="n">
-        <v>105.7096553890372</v>
+        <v>77.35592603662953</v>
       </c>
       <c r="Y43" t="n">
-        <v>98.58465335209479</v>
+        <v>93.19042554349667</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>330120.6239988174</v>
+        <v>310153.8822306904</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>471406.654376806</v>
+        <v>462617.6125550583</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>471406.654376806</v>
+        <v>462617.6125550583</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>471406.654376806</v>
+        <v>479986.3116580664</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>471406.654376806</v>
+        <v>479986.3116580665</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>463771.2626104958</v>
+        <v>479986.3116580665</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>552416.4074852272</v>
+        <v>568611.7879436982</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>552416.4074852272</v>
+        <v>568611.7879436982</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>552416.4074852272</v>
+        <v>568611.7879436982</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>552416.4074852272</v>
+        <v>568611.7879436982</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>519638.6912548581</v>
+        <v>546837.0759243623</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>757830.6133132604</v>
+        <v>757830.6133132605</v>
       </c>
       <c r="C2" t="n">
         <v>757830.6133132604</v>
       </c>
       <c r="D2" t="n">
-        <v>757830.6133132604</v>
+        <v>757830.6133132603</v>
       </c>
       <c r="E2" t="n">
-        <v>249596.6388876577</v>
+        <v>227209.6859961221</v>
       </c>
       <c r="F2" t="n">
-        <v>408008.2487054023</v>
+        <v>398153.8684810193</v>
       </c>
       <c r="G2" t="n">
-        <v>408008.2487054024</v>
+        <v>398153.8684810193</v>
       </c>
       <c r="H2" t="n">
-        <v>408008.2487054025</v>
+        <v>410186.990077513</v>
       </c>
       <c r="I2" t="n">
-        <v>408008.2487054024</v>
+        <v>410186.990077513</v>
       </c>
       <c r="J2" t="n">
-        <v>399447.3549068128</v>
+        <v>410186.990077513</v>
       </c>
       <c r="K2" t="n">
-        <v>498837.3658269657</v>
+        <v>509554.9483371609</v>
       </c>
       <c r="L2" t="n">
-        <v>498837.3658269657</v>
+        <v>509554.9483371608</v>
       </c>
       <c r="M2" t="n">
-        <v>498837.3658269658</v>
+        <v>509554.9483371608</v>
       </c>
       <c r="N2" t="n">
-        <v>498837.3658269658</v>
+        <v>509554.9483371609</v>
       </c>
       <c r="O2" t="n">
-        <v>462086.5930838248</v>
+        <v>485140.8772851778</v>
       </c>
       <c r="P2" t="n">
         <v>198888.7002331758</v>
@@ -26322,25 +26322,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>17600</v>
+        <v>9559.431483690014</v>
       </c>
       <c r="F3" t="n">
-        <v>57600</v>
+        <v>61957.87479744205</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>6194.680152033701</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14400</v>
+        <v>9559.431483690014</v>
       </c>
       <c r="K3" t="n">
-        <v>96000</v>
+        <v>100315.3822468785</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="C4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="D4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="E4" t="n">
-        <v>138796.5102383757</v>
+        <v>124455.3967726702</v>
       </c>
       <c r="F4" t="n">
-        <v>236543.679180778</v>
+        <v>229935.7331211011</v>
       </c>
       <c r="G4" t="n">
-        <v>236543.679180778</v>
+        <v>229935.733121101</v>
       </c>
       <c r="H4" t="n">
-        <v>236543.679180778</v>
+        <v>236559.5448698832</v>
       </c>
       <c r="I4" t="n">
-        <v>236543.679180778</v>
+        <v>236559.5448698832</v>
       </c>
       <c r="J4" t="n">
-        <v>231261.2182968092</v>
+        <v>236559.5448698832</v>
       </c>
       <c r="K4" t="n">
-        <v>292589.3759979829</v>
+        <v>297874.0950764132</v>
       </c>
       <c r="L4" t="n">
-        <v>292589.3759979829</v>
+        <v>297874.0950764132</v>
       </c>
       <c r="M4" t="n">
-        <v>292589.3759979829</v>
+        <v>297874.0950764132</v>
       </c>
       <c r="N4" t="n">
-        <v>292589.3759979829</v>
+        <v>297874.0950764132</v>
       </c>
       <c r="O4" t="n">
-        <v>269912.4775293628</v>
+        <v>282809.5027120303</v>
       </c>
       <c r="P4" t="n">
-        <v>107507.4055314464</v>
+        <v>106980.0603174001</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1849.518</v>
+        <v>1004.56480675292</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>8911.423221049232</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>8911.423221049232</v>
       </c>
       <c r="J5" t="n">
-        <v>7566.21</v>
+        <v>8911.423221049232</v>
       </c>
       <c r="K5" t="n">
-        <v>11601.522</v>
+        <v>12942.26983825757</v>
       </c>
       <c r="L5" t="n">
-        <v>11601.522</v>
+        <v>12942.26983825757</v>
       </c>
       <c r="M5" t="n">
-        <v>11601.522</v>
+        <v>12942.26983825757</v>
       </c>
       <c r="N5" t="n">
-        <v>11601.522</v>
+        <v>12942.26983825757</v>
       </c>
       <c r="O5" t="n">
-        <v>10088.28</v>
+        <v>11937.70503150465</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>271803.0227642952</v>
+        <v>272330.3679783417</v>
       </c>
       <c r="C6" t="n">
-        <v>271803.0227642952</v>
+        <v>272330.3679783416</v>
       </c>
       <c r="D6" t="n">
-        <v>271803.0227642952</v>
+        <v>272330.3679783415</v>
       </c>
       <c r="E6" t="n">
-        <v>91350.61064928201</v>
+        <v>92190.29293300894</v>
       </c>
       <c r="F6" t="n">
-        <v>105962.0835246243</v>
+        <v>98744.7750352906</v>
       </c>
       <c r="G6" t="n">
-        <v>163562.0835246244</v>
+        <v>160702.6498327327</v>
       </c>
       <c r="H6" t="n">
-        <v>163562.0835246244</v>
+        <v>158521.341834547</v>
       </c>
       <c r="I6" t="n">
-        <v>163562.0835246244</v>
+        <v>164716.0219865806</v>
       </c>
       <c r="J6" t="n">
-        <v>146219.9266100035</v>
+        <v>155156.5905028906</v>
       </c>
       <c r="K6" t="n">
-        <v>98646.46782898286</v>
+        <v>98423.20117561158</v>
       </c>
       <c r="L6" t="n">
-        <v>194646.4678289829</v>
+        <v>198738.58342249</v>
       </c>
       <c r="M6" t="n">
-        <v>194646.4678289829</v>
+        <v>198738.58342249</v>
       </c>
       <c r="N6" t="n">
-        <v>194646.467828983</v>
+        <v>198738.5834224901</v>
       </c>
       <c r="O6" t="n">
-        <v>182085.835554462</v>
+        <v>190393.6695416428</v>
       </c>
       <c r="P6" t="n">
-        <v>91381.29470172942</v>
+        <v>91908.63991577574</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J2" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="O2" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26849,31 +26849,31 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -26944,13 +26944,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -26962,31 +26962,31 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
-        <v>72</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="P2" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
     </row>
     <row r="3">
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
     </row>
   </sheetData>
@@ -27313,10 +27313,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>339.4748021157671</v>
@@ -27550,10 +27550,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>339.4748021157671</v>
@@ -27787,10 +27787,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>339.4748021157671</v>
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="R13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="16">
@@ -28407,31 +28407,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J16" t="n">
-        <v>93.35918011667277</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="19">
@@ -28644,31 +28644,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J19" t="n">
-        <v>93.35918011667277</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K19" t="n">
         <v>22.26949182588285</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="22">
@@ -28881,31 +28881,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J22" t="n">
-        <v>93.35918011667277</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K22" t="n">
         <v>22.26949182588285</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="25">
@@ -29118,31 +29118,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J25" t="n">
-        <v>93.35918011667277</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,25 +29276,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y29" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="30">
@@ -29513,19 +29513,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y30" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y31" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="33">
@@ -29750,19 +29750,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -29801,25 +29801,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="36">
@@ -29987,19 +29987,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="39">
@@ -30224,19 +30224,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="C41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="D41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="E41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="F41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="G41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="I41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="S41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="T41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="U41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="V41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="W41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="X41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="Y41" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="C42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="D42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="E42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="G42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30512,25 +30512,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="T42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="U42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="V42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="W42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="X42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="Y42" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="C43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="D43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="E43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="F43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="G43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="I43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="S43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="T43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="U43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="V43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="W43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="X43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="Y43" t="n">
-        <v>120</v>
+        <v>125.3942278085981</v>
       </c>
     </row>
     <row r="44">
@@ -36036,19 +36036,19 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36118,16 +36118,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -36197,16 +36197,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -36273,16 +36273,16 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -36361,16 +36361,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36434,16 +36434,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -36516,16 +36516,16 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36595,16 +36595,16 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36671,16 +36671,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -36747,16 +36747,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -36835,16 +36835,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36908,16 +36908,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -36984,16 +36984,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -37072,16 +37072,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37145,16 +37145,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -37224,16 +37224,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37303,19 +37303,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37382,16 +37382,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -37458,19 +37458,19 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37540,22 +37540,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37619,16 +37619,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -37698,16 +37698,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -37774,13 +37774,13 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -37789,7 +37789,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37856,16 +37856,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>22.03184491577681</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>22.95950154380951</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
